--- a/multiSchoolOutput/run_log.xlsx
+++ b/multiSchoolOutput/run_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,25 +459,295 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>Business School</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>205</v>
+      </c>
+      <c r="E2" t="n">
+        <v>205</v>
+      </c>
+      <c r="F2" t="n">
+        <v>350</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6113</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Centre for Open Learning</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>109</v>
+      </c>
+      <c r="E3" t="n">
+        <v>109</v>
+      </c>
+      <c r="F3" t="n">
+        <v>236</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6349</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>School of Economics</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>197</v>
+      </c>
+      <c r="E4" t="n">
+        <v>197</v>
+      </c>
+      <c r="F4" t="n">
+        <v>256</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6605</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>School of Health in Social Science</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>299</v>
+      </c>
+      <c r="E5" t="n">
+        <v>299</v>
+      </c>
+      <c r="F5" t="n">
+        <v>612</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7212</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Edinburgh Futures Institute</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>110</v>
+      </c>
+      <c r="E6" t="n">
+        <v>110</v>
+      </c>
+      <c r="F6" t="n">
+        <v>272</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7484</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>School of Social and Political Science</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>783</v>
+      </c>
+      <c r="E7" t="n">
+        <v>783</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1003</v>
+      </c>
+      <c r="G7" t="n">
+        <v>8483</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>School of Philosophy, Psychology and Language Sciences</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>399</v>
+      </c>
+      <c r="E8" t="n">
+        <v>396</v>
+      </c>
+      <c r="F8" t="n">
+        <v>501</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8969</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>School of Law</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>357</v>
+      </c>
+      <c r="E9" t="n">
+        <v>354</v>
+      </c>
+      <c r="F9" t="n">
+        <v>575</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9540</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>School of Literatures, Languages and Cultures</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1194</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1472</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11010</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>School of History, Classics and Archaeology</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>385</v>
+      </c>
+      <c r="E11" t="n">
+        <v>381</v>
+      </c>
+      <c r="F11" t="n">
+        <v>538</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11531</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Edinburgh Medical School</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>optimal</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>421</v>
       </c>
-      <c r="E2" t="n">
-        <v>421</v>
-      </c>
-      <c r="F2" t="n">
-        <v>794</v>
-      </c>
-      <c r="G2" t="n">
-        <v>792</v>
+      <c r="E12" t="n">
+        <v>420</v>
+      </c>
+      <c r="F12" t="n">
+        <v>789</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12290</v>
       </c>
     </row>
   </sheetData>

--- a/multiSchoolOutput/run_log.xlsx
+++ b/multiSchoolOutput/run_log.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Business School</t>
+          <t>Edinburgh Medical School</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,286 +468,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>205</v>
+        <v>421</v>
       </c>
       <c r="E2" t="n">
-        <v>205</v>
+        <v>420</v>
       </c>
       <c r="F2" t="n">
-        <v>350</v>
+        <v>789</v>
       </c>
       <c r="G2" t="n">
-        <v>6113</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Centre for Open Learning</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>109</v>
-      </c>
-      <c r="E3" t="n">
-        <v>109</v>
-      </c>
-      <c r="F3" t="n">
-        <v>236</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6349</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>School of Economics</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>197</v>
-      </c>
-      <c r="E4" t="n">
-        <v>197</v>
-      </c>
-      <c r="F4" t="n">
-        <v>256</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6605</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>School of Health in Social Science</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>299</v>
-      </c>
-      <c r="E5" t="n">
-        <v>299</v>
-      </c>
-      <c r="F5" t="n">
-        <v>612</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7212</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Edinburgh Futures Institute</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>110</v>
-      </c>
-      <c r="E6" t="n">
-        <v>110</v>
-      </c>
-      <c r="F6" t="n">
-        <v>272</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7484</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>School of Social and Political Science</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>783</v>
-      </c>
-      <c r="E7" t="n">
-        <v>783</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1003</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8483</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>School of Philosophy, Psychology and Language Sciences</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>399</v>
-      </c>
-      <c r="E8" t="n">
-        <v>396</v>
-      </c>
-      <c r="F8" t="n">
-        <v>501</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8969</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>School of Law</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>357</v>
-      </c>
-      <c r="E9" t="n">
-        <v>354</v>
-      </c>
-      <c r="F9" t="n">
-        <v>575</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9540</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>School of Literatures, Languages and Cultures</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1194</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1194</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1472</v>
-      </c>
-      <c r="G10" t="n">
-        <v>11010</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>School of History, Classics and Archaeology</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>385</v>
-      </c>
-      <c r="E11" t="n">
-        <v>381</v>
-      </c>
-      <c r="F11" t="n">
-        <v>538</v>
-      </c>
-      <c r="G11" t="n">
-        <v>11531</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Edinburgh Medical School</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>optimal</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>421</v>
-      </c>
-      <c r="E12" t="n">
-        <v>420</v>
-      </c>
-      <c r="F12" t="n">
-        <v>789</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12290</v>
+        <v>12135</v>
       </c>
     </row>
   </sheetData>
